--- a/data/trans_camb/P71_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 20,74</t>
+          <t>10,28; 20,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 21,82</t>
+          <t>10,74; 21,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 6,6</t>
+          <t>-5,64; 6,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 10,09</t>
+          <t>-1,1; 10,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,99</t>
+          <t>1,06; 12,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 4,14</t>
+          <t>-9,72; 5,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 13,73</t>
+          <t>6,26; 14,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,53</t>
+          <t>7,74; 15,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 3,67</t>
+          <t>-6,32; 3,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,07; 186,97</t>
+          <t>63,74; 184,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,71; 193,49</t>
+          <t>68,88; 194,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 54,24</t>
+          <t>-39,33; 57,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 53,46</t>
+          <t>-4,66; 52,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 63,43</t>
+          <t>4,88; 69,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 20,61</t>
+          <t>-43,37; 26,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54; 87,47</t>
+          <t>33,13; 94,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 100,33</t>
+          <t>41,1; 103,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 23,97</t>
+          <t>-34,74; 21,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 17,22</t>
+          <t>8,07; 16,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 22,22</t>
+          <t>12,47; 22,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 1,02</t>
+          <t>-8,64; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,59</t>
+          <t>7,39; 17,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,91</t>
+          <t>5,74; 16,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 30,32</t>
+          <t>-7,38; 36,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 16,1</t>
+          <t>9,27; 15,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 17,93</t>
+          <t>10,93; 18,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 21,84</t>
+          <t>-5,75; 20,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,72; 115,27</t>
+          <t>41,84; 110,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,97; 148,74</t>
+          <t>63,82; 147,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 6,88</t>
+          <t>-46,26; 7,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 94,22</t>
+          <t>31,44; 91,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,68; 85,65</t>
+          <t>24,08; 83,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 159,34</t>
+          <t>-34,48; 186,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,7; 93,2</t>
+          <t>44,41; 89,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,05; 102,54</t>
+          <t>52,98; 107,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 126,56</t>
+          <t>-29,76; 110,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,36; 24,85</t>
+          <t>15,33; 24,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,96; 22,43</t>
+          <t>13,18; 22,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,02</t>
+          <t>-5,3; 2,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,36</t>
+          <t>4,78; 14,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 16,77</t>
+          <t>6,53; 16,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -7,72</t>
+          <t>-17,26; -8,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 18,39</t>
+          <t>11,63; 18,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 17,76</t>
+          <t>10,76; 17,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; -3,84</t>
+          <t>-10,24; -3,89</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,88; 194,94</t>
+          <t>87,44; 192,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,37; 174,74</t>
+          <t>74,16; 177,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 23,25</t>
+          <t>-30,66; 20,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,57; 66,09</t>
+          <t>17,02; 65,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,34; 73,39</t>
+          <t>23,89; 74,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,76; -34,41</t>
+          <t>-61,75; -34,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,52; 97,64</t>
+          <t>52,98; 98,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,4; 95,38</t>
+          <t>49,26; 95,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -19,9</t>
+          <t>-46,78; -21,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,44; 22,86</t>
+          <t>12,19; 23,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 28,43</t>
+          <t>17,47; 27,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -1,45</t>
+          <t>-14,5; -1,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 13,38</t>
+          <t>1,17; 13,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,53; 21,41</t>
+          <t>10,14; 21,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -7,24</t>
+          <t>-16,43; -7,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,11</t>
+          <t>8,6; 16,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 23,37</t>
+          <t>15,28; 23,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -6,03</t>
+          <t>-15,47; -5,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>67,31; 168,83</t>
+          <t>61,74; 172,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92,88; 207,06</t>
+          <t>91,34; 204,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,25; -10,89</t>
+          <t>-76,78; -10,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 57,48</t>
+          <t>4,17; 56,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,05; 91,88</t>
+          <t>34,06; 92,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,43; -30,23</t>
+          <t>-55,3; -29,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,42; 84,16</t>
+          <t>37,17; 83,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>66,59; 122,77</t>
+          <t>65,17; 120,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,81; -30,81</t>
+          <t>-66,67; -30,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 13,72</t>
+          <t>0,28; 13,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 17,68</t>
+          <t>5,6; 18,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -0,91</t>
+          <t>-11,46; -0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 6,67</t>
+          <t>-5,98; 6,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,27</t>
+          <t>2,74; 16,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -3,99</t>
+          <t>-14,21; -3,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 8,0</t>
+          <t>-1,1; 7,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 14,82</t>
+          <t>6,23; 15,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -3,86</t>
+          <t>-11,13; -3,85</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,52; 65,86</t>
+          <t>0,96; 63,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20,17; 86,97</t>
+          <t>21,15; 91,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -4,02</t>
+          <t>-43,96; -3,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 25,62</t>
+          <t>-18,42; 25,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,62; 64,25</t>
+          <t>8,38; 62,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,0; -14,42</t>
+          <t>-43,36; -14,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 32,85</t>
+          <t>-3,82; 32,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19,99; 62,74</t>
+          <t>21,88; 64,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -16,53</t>
+          <t>-39,09; -15,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 7,17</t>
+          <t>-8,42; 6,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 13,09</t>
+          <t>-1,37; 12,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -7,81</t>
+          <t>-18,91; -7,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -6,42</t>
+          <t>-20,69; -6,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -2,14</t>
+          <t>-15,71; -1,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-42,29; -26,69</t>
+          <t>-42,42; -26,34</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,94; -2,43</t>
+          <t>-12,88; -2,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,57</t>
+          <t>-6,84; 3,2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-30,68; -19,59</t>
+          <t>-31,23; -20,06</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 37,9</t>
+          <t>-30,95; 30,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 64,5</t>
+          <t>-5,39; 64,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -40,65</t>
+          <t>-69,26; -40,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,08; -17,33</t>
+          <t>-47,11; -17,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,08; -5,7</t>
+          <t>-35,68; -4,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,53; -67,81</t>
+          <t>-93,64; -67,55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,43; -7,68</t>
+          <t>-36,6; -8,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 8,43</t>
+          <t>-19,62; 10,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-87,28; -64,3</t>
+          <t>-86,57; -63,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 4,75</t>
+          <t>-12,79; 5,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 5,5</t>
+          <t>-11,23; 5,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -15,78</t>
+          <t>-28,34; -15,53</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -3,43</t>
+          <t>-17,79; -3,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 1,22</t>
+          <t>-13,81; 1,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-29,04; -15,84</t>
+          <t>-29,23; -16,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -2,05</t>
+          <t>-14,05; -2,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 1,49</t>
+          <t>-10,31; 0,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-27,23; -17,71</t>
+          <t>-27,51; -17,87</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 18,06</t>
+          <t>-36,11; 18,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 20,73</t>
+          <t>-31,42; 19,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,86; -59,2</t>
+          <t>-80,63; -57,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -8,19</t>
+          <t>-39,26; -9,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 3,44</t>
+          <t>-30,7; 4,33</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-62,45; -43,0</t>
+          <t>-62,15; -44,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-33,85; -5,59</t>
+          <t>-34,29; -6,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 4,06</t>
+          <t>-25,17; 1,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -51,84</t>
+          <t>-66,3; -52,05</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10,51; 14,59</t>
+          <t>10,64; 14,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,53</t>
+          <t>13,32; 17,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -4,04</t>
+          <t>-9,08; -3,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,09</t>
+          <t>1,56; 6,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,37</t>
+          <t>5,45; 10,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -5,86</t>
+          <t>-14,3; -5,85</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,65</t>
+          <t>6,5; 9,7</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,91; 13,22</t>
+          <t>10,18; 13,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -5,45</t>
+          <t>-10,79; -5,63</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>54,41; 84,54</t>
+          <t>55,83; 85,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>69,88; 103,67</t>
+          <t>70,34; 103,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-47,77; -23,5</t>
+          <t>-49,51; -23,2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,04; 22,74</t>
+          <t>5,5; 22,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,02; 38,58</t>
+          <t>18,72; 38,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -21,82</t>
+          <t>-50,14; -21,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,03; 43,52</t>
+          <t>27,29; 43,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>41,19; 59,59</t>
+          <t>42,53; 60,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -23,19</t>
+          <t>-45,3; -24,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P71_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P71_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>0,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 20,41</t>
+          <t>9,85; 20,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 21,48</t>
+          <t>10,45; 21,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,81</t>
+          <t>-3,5; 10,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 10,03</t>
+          <t>-0,99; 10,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 12,89</t>
+          <t>0,85; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 5,4</t>
+          <t>-9,55; 4,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,2</t>
+          <t>6,07; 13,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,98</t>
+          <t>7,2; 15,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 3,38</t>
+          <t>-4,57; 5,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,67%</t>
+          <t>-13,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-9,63%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,74; 184,6</t>
+          <t>66,58; 193,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,88; 194,98</t>
+          <t>65,34; 187,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 57,8</t>
+          <t>-23,79; 90,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 52,47</t>
+          <t>-4,23; 56,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 69,29</t>
+          <t>3,69; 72,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 26,46</t>
+          <t>-41,18; 22,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,13; 94,11</t>
+          <t>32,02; 89,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,1; 103,12</t>
+          <t>38,66; 98,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 21,48</t>
+          <t>-24,77; 32,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,94</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>-3,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 16,83</t>
+          <t>8,05; 17,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 22,39</t>
+          <t>12,93; 22,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 1,44</t>
+          <t>-7,56; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 17,76</t>
+          <t>6,88; 17,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 16,03</t>
+          <t>5,61; 16,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 36,24</t>
+          <t>-8,66; 1,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 15,74</t>
+          <t>9,13; 16,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 18,45</t>
+          <t>11,26; 18,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 20,18</t>
+          <t>-6,66; 0,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,04%</t>
+          <t>-19,5%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>-18,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>-17,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,84; 110,32</t>
+          <t>43,94; 119,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,82; 147,48</t>
+          <t>67,36; 152,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 7,97</t>
+          <t>-41,12; 10,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,44; 91,53</t>
+          <t>29,11; 92,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,08; 83,21</t>
+          <t>23,33; 85,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 186,16</t>
+          <t>-37,86; 9,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,41; 89,98</t>
+          <t>43,59; 92,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,98; 107,2</t>
+          <t>54,12; 103,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 110,27</t>
+          <t>-32,52; 2,04</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,24</t>
+          <t>-10,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-4,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 24,6</t>
+          <t>15,03; 24,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,54</t>
+          <t>13,07; 22,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,67</t>
+          <t>-3,37; 5,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,95</t>
+          <t>5,16; 14,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 16,9</t>
+          <t>6,62; 16,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -8,01</t>
+          <t>-14,38; -6,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,63; 18,27</t>
+          <t>10,86; 18,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 17,99</t>
+          <t>11,02; 18,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -3,89</t>
+          <t>-7,66; -1,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,9%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-47,85%</t>
+          <t>-39,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,08%</t>
+          <t>-23,2%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87,44; 192,4</t>
+          <t>86,79; 191,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,16; 177,47</t>
+          <t>74,33; 174,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 20,99</t>
+          <t>-20,2; 46,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,02; 65,41</t>
+          <t>18,16; 65,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,89; 74,59</t>
+          <t>23,11; 71,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,75; -34,32</t>
+          <t>-50,77; -25,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,98; 98,42</t>
+          <t>48,02; 96,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,26; 95,56</t>
+          <t>49,8; 96,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -21,23</t>
+          <t>-35,08; -9,59</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,94</t>
+          <t>-11,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,68</t>
+          <t>-6,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 23,32</t>
+          <t>12,51; 22,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,47; 27,72</t>
+          <t>17,23; 27,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -1,54</t>
+          <t>-6,24; 2,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,16</t>
+          <t>1,79; 13,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 21,7</t>
+          <t>10,39; 21,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,43; -7,08</t>
+          <t>-15,58; -6,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 16,45</t>
+          <t>8,44; 16,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,28; 23,24</t>
+          <t>15,97; 23,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -5,88</t>
+          <t>-9,65; -3,27</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-42,72%</t>
+          <t>-12,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,25%</t>
+          <t>-42,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-45,78%</t>
+          <t>-30,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,74; 172,69</t>
+          <t>66,65; 168,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,34; 204,61</t>
+          <t>93,01; 213,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,78; -10,72</t>
+          <t>-34,05; 17,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 56,62</t>
+          <t>5,76; 57,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,06; 92,98</t>
+          <t>34,19; 89,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,3; -29,79</t>
+          <t>-52,84; -29,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,17; 83,23</t>
+          <t>36,46; 85,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>65,17; 120,02</t>
+          <t>68,15; 123,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,67; -30,49</t>
+          <t>-41,92; -16,72</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-5,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,0</t>
+          <t>-8,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,64</t>
+          <t>-7,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 13,15</t>
+          <t>0,44; 13,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,6; 18,25</t>
+          <t>5,54; 17,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -0,59</t>
+          <t>-10,51; -0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,75</t>
+          <t>-5,78; 6,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 16,13</t>
+          <t>1,96; 15,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,21; -3,94</t>
+          <t>-14,04; -3,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 7,64</t>
+          <t>-1,31; 7,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 15,22</t>
+          <t>5,63; 15,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,13; -3,85</t>
+          <t>-10,77; -3,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-26,12%</t>
+          <t>-23,22%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,09%</t>
+          <t>-30,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,14%</t>
+          <t>-27,23%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,96; 63,79</t>
+          <t>1,51; 64,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21,15; 91,22</t>
+          <t>20,73; 90,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,96; -3,14</t>
+          <t>-40,23; -1,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 25,69</t>
+          <t>-18,4; 26,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,38; 62,97</t>
+          <t>5,65; 62,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,36; -14,87</t>
+          <t>-42,6; -14,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 32,3</t>
+          <t>-4,98; 32,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,88; 64,72</t>
+          <t>19,47; 65,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,09; -15,68</t>
+          <t>-37,54; -15,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-13,44</t>
+          <t>-13,16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-32,61</t>
+          <t>-28,36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-23,94</t>
+          <t>-21,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,11</t>
+          <t>-8,17; 6,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 12,69</t>
+          <t>-1,41; 13,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -7,87</t>
+          <t>-18,94; -8,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -6,35</t>
+          <t>-20,69; -7,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -1,89</t>
+          <t>-15,61; -2,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-42,42; -26,34</t>
+          <t>-34,25; -22,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,88; -2,68</t>
+          <t>-12,6; -2,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,2</t>
+          <t>-6,92; 2,91</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-31,23; -20,06</t>
+          <t>-25,81; -17,7</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-57,82%</t>
+          <t>-56,65%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-80,29%</t>
+          <t>-69,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-73,39%</t>
+          <t>-65,66%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 30,1</t>
+          <t>-29,97; 31,62</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 64,03</t>
+          <t>-6,88; 64,37</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -40,78</t>
+          <t>-68,91; -40,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -17,35</t>
+          <t>-47,9; -18,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,68; -4,59</t>
+          <t>-36,0; -6,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,64; -67,55</t>
+          <t>-76,32; -62,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -8,85</t>
+          <t>-36,27; -8,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 10,0</t>
+          <t>-19,68; 9,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,57; -63,8</t>
+          <t>-72,18; -59,15</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-22,39</t>
+          <t>-22,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-22,4</t>
+          <t>-22,06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-22,61</t>
+          <t>-22,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 5,11</t>
+          <t>-12,56; 4,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 5,24</t>
+          <t>-11,23; 4,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -15,53</t>
+          <t>-29,32; -15,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -3,55</t>
+          <t>-17,72; -2,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 1,7</t>
+          <t>-13,26; 1,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-29,23; -16,3</t>
+          <t>-28,31; -15,53</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -2,27</t>
+          <t>-13,32; -1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 0,5</t>
+          <t>-10,66; 0,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-27,51; -17,87</t>
+          <t>-26,96; -17,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-71,85%</t>
+          <t>-72,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,66%</t>
+          <t>-52,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-59,97%</t>
+          <t>-59,6%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 18,85</t>
+          <t>-35,84; 17,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 19,02</t>
+          <t>-31,15; 17,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,63; -57,75</t>
+          <t>-80,68; -57,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-39,26; -9,76</t>
+          <t>-39,16; -8,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 4,33</t>
+          <t>-29,64; 5,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-62,15; -44,1</t>
+          <t>-60,93; -42,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,29; -6,56</t>
+          <t>-33,08; -4,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 1,45</t>
+          <t>-26,07; 2,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -52,05</t>
+          <t>-65,59; -52,01</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-3,75</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-10,96</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-8,54</t>
+          <t>-7,38</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,75</t>
+          <t>10,5; 14,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,71</t>
+          <t>13,03; 17,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -3,95</t>
+          <t>-5,71; -1,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,01</t>
+          <t>1,62; 6,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,23</t>
+          <t>5,67; 10,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -5,85</t>
+          <t>-12,89; -9,03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,7</t>
+          <t>6,64; 9,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,31</t>
+          <t>9,96; 13,08</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -5,63</t>
+          <t>-8,89; -5,98</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-32,9%</t>
+          <t>-20,76%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-40,07%</t>
+          <t>-39,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-37,1%</t>
+          <t>-32,07%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>55,83; 85,44</t>
+          <t>54,05; 86,69</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>70,34; 103,99</t>
+          <t>68,16; 103,49</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-49,51; -23,2</t>
+          <t>-30,19; -11,31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,88</t>
+          <t>5,37; 22,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,72; 38,62</t>
+          <t>19,59; 37,85</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,14; -21,34</t>
+          <t>-44,76; -33,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,29; 43,99</t>
+          <t>27,52; 42,98</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>42,53; 60,45</t>
+          <t>41,99; 58,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -24,3</t>
+          <t>-37,09; -26,92</t>
         </is>
       </c>
     </row>
